--- a/Sindhi Muslim/Student Attendance/Class 1/Class 1 - Monthly Attendance - October-2024.xlsx
+++ b/Sindhi Muslim/Student Attendance/Class 1/Class 1 - Monthly Attendance - October-2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Student Attendance\Class 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Student Attendance\Class 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E81573-DE5A-4902-B3AC-88BFDB818ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D349DA7A-EE92-43ED-BDD2-EB0573928001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="542" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" tabRatio="542" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Class-I (Girls)" sheetId="4" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="132">
   <si>
     <t>S.No</t>
   </si>
@@ -419,6 +419,18 @@
   </si>
   <si>
     <t>Monthly Attendence Month of October-2024</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -691,34 +703,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -733,16 +718,87 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="22">
     <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1199,99 +1255,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
-      <c r="V1" s="22"/>
-      <c r="W1" s="22"/>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="22"/>
-      <c r="AB1" s="22"/>
-      <c r="AC1" s="22"/>
-      <c r="AD1" s="22"/>
-      <c r="AE1" s="22"/>
-      <c r="AF1" s="22"/>
-      <c r="AG1" s="22"/>
-      <c r="AH1" s="22"/>
-      <c r="AI1" s="22"/>
-      <c r="AJ1" s="22"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="34"/>
+      <c r="AD1" s="34"/>
+      <c r="AE1" s="34"/>
+      <c r="AF1" s="34"/>
+      <c r="AG1" s="34"/>
+      <c r="AH1" s="34"/>
+      <c r="AI1" s="34"/>
+      <c r="AJ1" s="34"/>
     </row>
     <row r="2" spans="1:42" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="29"/>
-      <c r="AB2" s="29"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="29"/>
-      <c r="AE2" s="29"/>
-      <c r="AF2" s="29"/>
-      <c r="AG2" s="29"/>
-      <c r="AH2" s="29"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="29"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
+      <c r="T2" s="33"/>
+      <c r="U2" s="33"/>
+      <c r="V2" s="33"/>
+      <c r="W2" s="33"/>
+      <c r="X2" s="33"/>
+      <c r="Y2" s="33"/>
+      <c r="Z2" s="33"/>
+      <c r="AA2" s="33"/>
+      <c r="AB2" s="33"/>
+      <c r="AC2" s="33"/>
+      <c r="AD2" s="33"/>
+      <c r="AE2" s="33"/>
+      <c r="AF2" s="33"/>
+      <c r="AG2" s="33"/>
+      <c r="AH2" s="33"/>
+      <c r="AI2" s="33"/>
+      <c r="AJ2" s="33"/>
     </row>
     <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="31" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -1418,25 +1474,25 @@
         <f t="shared" si="1"/>
         <v>Thu</v>
       </c>
-      <c r="AK3" s="25" t="s">
+      <c r="AK3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="AL3" s="25" t="s">
+      <c r="AL3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="AM3" s="26" t="s">
+      <c r="AM3" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="AN3" s="27"/>
+      <c r="AN3" s="29"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
     </row>
     <row r="4" spans="1:42" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="24"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
       <c r="F4" s="21">
         <v>45566</v>
       </c>
@@ -1530,8 +1586,8 @@
       <c r="AJ4" s="21">
         <v>45596</v>
       </c>
-      <c r="AK4" s="25"/>
-      <c r="AL4" s="25"/>
+      <c r="AK4" s="27"/>
+      <c r="AL4" s="27"/>
       <c r="AM4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1555,52 +1611,106 @@
       <c r="E5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="30"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="33" t="s">
+      <c r="F5" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H5" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I5" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J5" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="K5" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="L5" s="11"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="33" t="s">
+      <c r="L5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R5" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="S5" s="11"/>
-      <c r="T5" s="30"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="31"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="33" t="s">
+      <c r="S5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y5" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="Z5" s="11"/>
-      <c r="AA5" s="30"/>
-      <c r="AB5" s="11"/>
-      <c r="AC5" s="11"/>
-      <c r="AD5" s="11"/>
-      <c r="AE5" s="11"/>
-      <c r="AF5" s="33" t="s">
+      <c r="Z5" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF5" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="AG5" s="11"/>
-      <c r="AH5" s="11"/>
-      <c r="AI5" s="30"/>
-      <c r="AJ5" s="11"/>
+      <c r="AG5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ5" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK5" s="5">
         <f t="shared" ref="AK5:AK28" si="2">COUNTIF(F5:AJ5,"P")</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL5" s="5">
         <f t="shared" ref="AL5:AL28" si="3">COUNTIF(F5:AJ5,"A")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM5" s="5" t="s">
         <v>8</v>
@@ -1613,7 +1723,7 @@
       </c>
       <c r="AP5" s="3"/>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -1627,44 +1737,98 @@
       <c r="E6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="30"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="34"/>
-      <c r="S6" s="11"/>
-      <c r="T6" s="30"/>
-      <c r="U6" s="11"/>
-      <c r="V6" s="31"/>
-      <c r="W6" s="11"/>
-      <c r="X6" s="11"/>
-      <c r="Y6" s="34"/>
-      <c r="Z6" s="11"/>
-      <c r="AA6" s="30"/>
-      <c r="AB6" s="11"/>
-      <c r="AC6" s="11"/>
-      <c r="AD6" s="11"/>
-      <c r="AE6" s="11"/>
-      <c r="AF6" s="34"/>
-      <c r="AG6" s="11"/>
-      <c r="AH6" s="11"/>
-      <c r="AI6" s="30"/>
-      <c r="AJ6" s="11"/>
+      <c r="F6" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I6" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="J6" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="K6" s="25"/>
+      <c r="L6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="R6" s="25"/>
+      <c r="S6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X6" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y6" s="25"/>
+      <c r="Z6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC6" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD6" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE6" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF6" s="25"/>
+      <c r="AG6" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH6" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI6" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AJ6" s="11" t="s">
+        <v>129</v>
+      </c>
       <c r="AK6" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AL6" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AM6" s="5" t="s">
         <v>10</v>
@@ -1675,7 +1839,7 @@
       <c r="AO6" s="3"/>
       <c r="AP6" s="3"/>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>3</v>
       </c>
@@ -1689,51 +1853,105 @@
       <c r="E7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="30"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="34"/>
-      <c r="S7" s="11"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="11"/>
-      <c r="V7" s="31"/>
-      <c r="W7" s="11"/>
-      <c r="X7" s="11"/>
-      <c r="Y7" s="34"/>
-      <c r="Z7" s="11"/>
-      <c r="AA7" s="30"/>
-      <c r="AB7" s="11"/>
-      <c r="AC7" s="11"/>
-      <c r="AD7" s="11"/>
-      <c r="AE7" s="11"/>
-      <c r="AF7" s="34"/>
-      <c r="AG7" s="11"/>
-      <c r="AH7" s="11"/>
-      <c r="AI7" s="30"/>
-      <c r="AJ7" s="11"/>
+      <c r="F7" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H7" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I7" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J7" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="K7" s="25"/>
+      <c r="L7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R7" s="25"/>
+      <c r="S7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T7" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y7" s="25"/>
+      <c r="Z7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF7" s="25"/>
+      <c r="AG7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ7" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK7" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL7" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM7" s="3"/>
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
       <c r="AP7" s="3"/>
     </row>
-    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -1747,53 +1965,107 @@
       <c r="E8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="30"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="34"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="30"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="31"/>
-      <c r="W8" s="11"/>
-      <c r="X8" s="11"/>
-      <c r="Y8" s="34"/>
-      <c r="Z8" s="11"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="11"/>
-      <c r="AC8" s="11"/>
-      <c r="AD8" s="11"/>
-      <c r="AE8" s="11"/>
-      <c r="AF8" s="34"/>
-      <c r="AG8" s="11"/>
-      <c r="AH8" s="11"/>
-      <c r="AI8" s="30"/>
-      <c r="AJ8" s="11"/>
+      <c r="F8" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="I8" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="J8" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="K8" s="25"/>
+      <c r="L8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R8" s="25"/>
+      <c r="S8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V8" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="W8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X8" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y8" s="25"/>
+      <c r="Z8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD8" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF8" s="25"/>
+      <c r="AG8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ8" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK8" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL8" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AM8" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="AM8" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="AN8" s="27"/>
-      <c r="AO8" s="27"/>
-      <c r="AP8" s="28"/>
+      <c r="AN8" s="29"/>
+      <c r="AO8" s="29"/>
+      <c r="AP8" s="30"/>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>5</v>
       </c>
@@ -1807,44 +2079,98 @@
       <c r="E9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="30"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="34"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="30"/>
-      <c r="U9" s="11"/>
-      <c r="V9" s="31"/>
-      <c r="W9" s="11"/>
-      <c r="X9" s="11"/>
-      <c r="Y9" s="34"/>
-      <c r="Z9" s="11"/>
-      <c r="AA9" s="30"/>
-      <c r="AB9" s="11"/>
-      <c r="AC9" s="11"/>
-      <c r="AD9" s="11"/>
-      <c r="AE9" s="11"/>
-      <c r="AF9" s="34"/>
-      <c r="AG9" s="11"/>
-      <c r="AH9" s="11"/>
-      <c r="AI9" s="30"/>
-      <c r="AJ9" s="11"/>
+      <c r="F9" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I9" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J9" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="K9" s="25"/>
+      <c r="L9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R9" s="25"/>
+      <c r="S9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y9" s="25"/>
+      <c r="Z9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF9" s="25"/>
+      <c r="AG9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ9" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK9" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL9" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM9" s="5" t="s">
         <v>12</v>
@@ -1859,7 +2185,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>6</v>
       </c>
@@ -1873,44 +2199,98 @@
       <c r="E10" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="30"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="34"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="30"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="31"/>
-      <c r="W10" s="11"/>
-      <c r="X10" s="11"/>
-      <c r="Y10" s="34"/>
-      <c r="Z10" s="11"/>
-      <c r="AA10" s="30"/>
-      <c r="AB10" s="11"/>
-      <c r="AC10" s="11"/>
-      <c r="AD10" s="11"/>
-      <c r="AE10" s="11"/>
-      <c r="AF10" s="34"/>
-      <c r="AG10" s="11"/>
-      <c r="AH10" s="11"/>
-      <c r="AI10" s="30"/>
-      <c r="AJ10" s="11"/>
+      <c r="F10" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H10" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J10" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="K10" s="25"/>
+      <c r="L10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="N10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q10" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="R10" s="25"/>
+      <c r="S10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V10" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="W10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y10" s="25"/>
+      <c r="Z10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD10" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF10" s="25"/>
+      <c r="AG10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ10" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK10" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AM10" s="5" t="s">
         <v>16</v>
@@ -1928,7 +2308,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>7</v>
       </c>
@@ -1942,62 +2322,116 @@
       <c r="E11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="30"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="34"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="30"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="31"/>
-      <c r="W11" s="11"/>
-      <c r="X11" s="11"/>
-      <c r="Y11" s="34"/>
-      <c r="Z11" s="11"/>
-      <c r="AA11" s="30"/>
-      <c r="AB11" s="11"/>
-      <c r="AC11" s="11"/>
-      <c r="AD11" s="11"/>
-      <c r="AE11" s="11"/>
-      <c r="AF11" s="34"/>
-      <c r="AG11" s="11"/>
-      <c r="AH11" s="11"/>
-      <c r="AI11" s="30"/>
-      <c r="AJ11" s="11"/>
+      <c r="F11" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I11" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J11" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="K11" s="25"/>
+      <c r="L11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P11" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q11" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="R11" s="25"/>
+      <c r="S11" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="T11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y11" s="25"/>
+      <c r="Z11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF11" s="25"/>
+      <c r="AG11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ11" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK11" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL11" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM11" s="5" t="s">
         <v>17</v>
       </c>
       <c r="AN11" s="12">
         <f>AK6+AK7+AK8+AK11+AK12+AK13+AK15+AK19+AK20+AK21+AK22+AK23+AK24+AK25+AK26+AK28</f>
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="AO11" s="12">
         <f>AK5+AK9+AK10+AK14+AK16+AK17+AK18+AK27</f>
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="AP11" s="12">
         <f>AN11+AO11</f>
-        <v>0</v>
+        <v>525</v>
       </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="12">
         <v>8</v>
       </c>
@@ -2011,62 +2445,116 @@
       <c r="E12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="30"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="34"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="30"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="31"/>
-      <c r="W12" s="11"/>
-      <c r="X12" s="11"/>
-      <c r="Y12" s="34"/>
-      <c r="Z12" s="11"/>
-      <c r="AA12" s="30"/>
-      <c r="AB12" s="11"/>
-      <c r="AC12" s="11"/>
-      <c r="AD12" s="11"/>
-      <c r="AE12" s="11"/>
-      <c r="AF12" s="34"/>
-      <c r="AG12" s="11"/>
-      <c r="AH12" s="11"/>
-      <c r="AI12" s="30"/>
-      <c r="AJ12" s="11"/>
+      <c r="F12" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I12" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J12" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="K12" s="25"/>
+      <c r="L12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R12" s="25"/>
+      <c r="S12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y12" s="25"/>
+      <c r="Z12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE12" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF12" s="25"/>
+      <c r="AG12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ12" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK12" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL12" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM12" s="5" t="s">
         <v>18</v>
       </c>
       <c r="AN12" s="12">
         <f>AN11/AN10</f>
-        <v>0</v>
+        <v>0.71255060728744934</v>
       </c>
       <c r="AO12" s="12">
         <f>AO11/AO10</f>
-        <v>0</v>
+        <v>0.31684981684981683</v>
       </c>
       <c r="AP12" s="12">
         <f>AP11/AP10</f>
-        <v>0</v>
+        <v>0.50480769230769229</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>9</v>
       </c>
@@ -2080,51 +2568,105 @@
       <c r="E13" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="30"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="34"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="30"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="31"/>
-      <c r="W13" s="11"/>
-      <c r="X13" s="11"/>
-      <c r="Y13" s="34"/>
-      <c r="Z13" s="11"/>
-      <c r="AA13" s="30"/>
-      <c r="AB13" s="11"/>
-      <c r="AC13" s="11"/>
-      <c r="AD13" s="11"/>
-      <c r="AE13" s="11"/>
-      <c r="AF13" s="34"/>
-      <c r="AG13" s="11"/>
-      <c r="AH13" s="11"/>
-      <c r="AI13" s="30"/>
-      <c r="AJ13" s="11"/>
+      <c r="F13" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H13" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J13" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="K13" s="25"/>
+      <c r="L13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R13" s="25"/>
+      <c r="S13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X13" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y13" s="25"/>
+      <c r="Z13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF13" s="25"/>
+      <c r="AG13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ13" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK13" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL13" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM13" s="3"/>
       <c r="AN13" s="17"/>
       <c r="AO13" s="17"/>
       <c r="AP13" s="17"/>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="12">
         <v>10</v>
       </c>
@@ -2138,40 +2680,94 @@
       <c r="E14" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="30"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="34"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="30"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="31"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="11"/>
-      <c r="Y14" s="34"/>
-      <c r="Z14" s="11"/>
-      <c r="AA14" s="30"/>
-      <c r="AB14" s="11"/>
-      <c r="AC14" s="11"/>
-      <c r="AD14" s="11"/>
-      <c r="AE14" s="11"/>
-      <c r="AF14" s="34"/>
-      <c r="AG14" s="11"/>
-      <c r="AH14" s="11"/>
-      <c r="AI14" s="30"/>
-      <c r="AJ14" s="11"/>
+      <c r="F14" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I14" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J14" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="K14" s="25"/>
+      <c r="L14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R14" s="25"/>
+      <c r="S14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y14" s="25"/>
+      <c r="Z14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF14" s="25"/>
+      <c r="AG14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ14" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK14" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL14" s="5">
         <f t="shared" si="3"/>
@@ -2182,7 +2778,7 @@
       <c r="AO14" s="19"/>
       <c r="AP14" s="19"/>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>11</v>
       </c>
@@ -2196,51 +2792,105 @@
       <c r="E15" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="30"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="11"/>
-      <c r="T15" s="30"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="31"/>
-      <c r="W15" s="11"/>
-      <c r="X15" s="11"/>
-      <c r="Y15" s="34"/>
-      <c r="Z15" s="11"/>
-      <c r="AA15" s="30"/>
-      <c r="AB15" s="11"/>
-      <c r="AC15" s="11"/>
-      <c r="AD15" s="11"/>
-      <c r="AE15" s="11"/>
-      <c r="AF15" s="34"/>
-      <c r="AG15" s="11"/>
-      <c r="AH15" s="11"/>
-      <c r="AI15" s="30"/>
-      <c r="AJ15" s="11"/>
+      <c r="F15" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H15" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="I15" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="J15" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="K15" s="25"/>
+      <c r="L15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O15" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="P15" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q15" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="R15" s="25"/>
+      <c r="S15" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="T15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U15" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="V15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X15" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y15" s="25"/>
+      <c r="Z15" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA15" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB15" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AC15" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD15" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE15" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF15" s="25"/>
+      <c r="AG15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH15" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ15" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK15" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AL15" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AM15" s="3"/>
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
     </row>
-    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="12">
         <v>12</v>
       </c>
@@ -2254,53 +2904,107 @@
       <c r="E16" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="30"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="34"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="30"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="31"/>
-      <c r="W16" s="11"/>
-      <c r="X16" s="11"/>
-      <c r="Y16" s="34"/>
-      <c r="Z16" s="11"/>
-      <c r="AA16" s="30"/>
-      <c r="AB16" s="11"/>
-      <c r="AC16" s="11"/>
-      <c r="AD16" s="11"/>
-      <c r="AE16" s="11"/>
-      <c r="AF16" s="34"/>
-      <c r="AG16" s="11"/>
-      <c r="AH16" s="11"/>
-      <c r="AI16" s="30"/>
-      <c r="AJ16" s="11"/>
+      <c r="F16" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I16" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J16" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="K16" s="25"/>
+      <c r="L16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="N16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R16" s="25"/>
+      <c r="S16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y16" s="25"/>
+      <c r="Z16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA16" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB16" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="AC16" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD16" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF16" s="25"/>
+      <c r="AG16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ16" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK16" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL16" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AM16" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="AN16" s="27"/>
-      <c r="AO16" s="27"/>
-      <c r="AP16" s="28"/>
+      <c r="AN16" s="29"/>
+      <c r="AO16" s="29"/>
+      <c r="AP16" s="30"/>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>13</v>
       </c>
@@ -2314,44 +3018,98 @@
       <c r="E17" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="30"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="34"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="30"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="31"/>
-      <c r="W17" s="11"/>
-      <c r="X17" s="11"/>
-      <c r="Y17" s="34"/>
-      <c r="Z17" s="11"/>
-      <c r="AA17" s="30"/>
-      <c r="AB17" s="11"/>
-      <c r="AC17" s="11"/>
-      <c r="AD17" s="11"/>
-      <c r="AE17" s="11"/>
-      <c r="AF17" s="34"/>
-      <c r="AG17" s="11"/>
-      <c r="AH17" s="11"/>
-      <c r="AI17" s="30"/>
-      <c r="AJ17" s="11"/>
+      <c r="F17" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="H17" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I17" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="J17" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="K17" s="25"/>
+      <c r="L17" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="N17" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="O17" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="P17" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q17" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="R17" s="25"/>
+      <c r="S17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y17" s="25"/>
+      <c r="Z17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD17" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF17" s="25"/>
+      <c r="AG17" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH17" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI17" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AJ17" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK17" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AL17" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AM17" s="5" t="s">
         <v>12</v>
@@ -2366,7 +3124,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A18" s="12">
         <v>14</v>
       </c>
@@ -2380,44 +3138,98 @@
       <c r="E18" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="30"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="34"/>
-      <c r="S18" s="11"/>
-      <c r="T18" s="30"/>
-      <c r="U18" s="11"/>
-      <c r="V18" s="31"/>
-      <c r="W18" s="11"/>
-      <c r="X18" s="11"/>
-      <c r="Y18" s="34"/>
-      <c r="Z18" s="11"/>
-      <c r="AA18" s="30"/>
-      <c r="AB18" s="11"/>
-      <c r="AC18" s="11"/>
-      <c r="AD18" s="11"/>
-      <c r="AE18" s="11"/>
-      <c r="AF18" s="34"/>
-      <c r="AG18" s="11"/>
-      <c r="AH18" s="11"/>
-      <c r="AI18" s="30"/>
-      <c r="AJ18" s="11"/>
+      <c r="F18" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="H18" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="I18" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="J18" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="K18" s="25"/>
+      <c r="L18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R18" s="25"/>
+      <c r="S18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y18" s="25"/>
+      <c r="Z18" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA18" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB18" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AC18" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD18" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE18" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF18" s="25"/>
+      <c r="AG18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ18" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK18" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AL18" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM18" s="5" t="s">
         <v>16</v>
@@ -2435,7 +3247,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>15</v>
       </c>
@@ -2449,62 +3261,116 @@
       <c r="E19" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="30"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="34"/>
-      <c r="S19" s="11"/>
-      <c r="T19" s="30"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="31"/>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11"/>
-      <c r="Y19" s="34"/>
-      <c r="Z19" s="11"/>
-      <c r="AA19" s="30"/>
-      <c r="AB19" s="11"/>
-      <c r="AC19" s="11"/>
-      <c r="AD19" s="11"/>
-      <c r="AE19" s="11"/>
-      <c r="AF19" s="34"/>
-      <c r="AG19" s="11"/>
-      <c r="AH19" s="11"/>
-      <c r="AI19" s="30"/>
-      <c r="AJ19" s="11"/>
+      <c r="F19" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="H19" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I19" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J19" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="K19" s="25"/>
+      <c r="L19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R19" s="25"/>
+      <c r="S19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y19" s="25"/>
+      <c r="Z19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE19" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF19" s="25"/>
+      <c r="AG19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ19" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK19" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL19" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM19" s="5" t="s">
         <v>19</v>
       </c>
       <c r="AN19" s="12">
         <f>AN18-AN11</f>
-        <v>494</v>
+        <v>142</v>
       </c>
       <c r="AO19" s="12">
         <f>AO18-AO11</f>
-        <v>546</v>
+        <v>373</v>
       </c>
       <c r="AP19" s="12">
         <f>AN19+AO19</f>
-        <v>1040</v>
+        <v>515</v>
       </c>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A20" s="12">
         <v>16</v>
       </c>
@@ -2518,62 +3384,116 @@
       <c r="E20" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F20" s="30"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="34"/>
-      <c r="S20" s="11"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="11"/>
-      <c r="V20" s="31"/>
-      <c r="W20" s="11"/>
-      <c r="X20" s="11"/>
-      <c r="Y20" s="34"/>
-      <c r="Z20" s="11"/>
-      <c r="AA20" s="30"/>
-      <c r="AB20" s="11"/>
-      <c r="AC20" s="11"/>
-      <c r="AD20" s="11"/>
-      <c r="AE20" s="11"/>
-      <c r="AF20" s="34"/>
-      <c r="AG20" s="11"/>
-      <c r="AH20" s="11"/>
-      <c r="AI20" s="30"/>
-      <c r="AJ20" s="11"/>
+      <c r="F20" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H20" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I20" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J20" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="K20" s="25"/>
+      <c r="L20" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q20" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="R20" s="25"/>
+      <c r="S20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X20" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y20" s="25"/>
+      <c r="Z20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE20" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF20" s="25"/>
+      <c r="AG20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ20" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK20" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL20" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM20" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AN20" s="20">
         <f>AN19/AN18</f>
-        <v>1</v>
+        <v>0.2874493927125506</v>
       </c>
       <c r="AO20" s="20">
         <f>AO19/AO18</f>
-        <v>1</v>
+        <v>0.68315018315018317</v>
       </c>
       <c r="AP20" s="20">
         <f>AP19/AP18</f>
-        <v>1</v>
+        <v>0.49519230769230771</v>
       </c>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>17</v>
       </c>
@@ -2587,47 +3507,101 @@
       <c r="E21" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="30"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="11"/>
-      <c r="R21" s="34"/>
-      <c r="S21" s="11"/>
-      <c r="T21" s="30"/>
-      <c r="U21" s="11"/>
-      <c r="V21" s="31"/>
-      <c r="W21" s="11"/>
-      <c r="X21" s="11"/>
-      <c r="Y21" s="34"/>
-      <c r="Z21" s="11"/>
-      <c r="AA21" s="30"/>
-      <c r="AB21" s="11"/>
-      <c r="AC21" s="11"/>
-      <c r="AD21" s="11"/>
-      <c r="AE21" s="11"/>
-      <c r="AF21" s="34"/>
-      <c r="AG21" s="11"/>
-      <c r="AH21" s="11"/>
-      <c r="AI21" s="30"/>
-      <c r="AJ21" s="11"/>
+      <c r="F21" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H21" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I21" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J21" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="K21" s="25"/>
+      <c r="L21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R21" s="25"/>
+      <c r="S21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W21" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="X21" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y21" s="25"/>
+      <c r="Z21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA21" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF21" s="25"/>
+      <c r="AG21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI21" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AJ21" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK21" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL21" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A22" s="12">
         <v>18</v>
       </c>
@@ -2641,47 +3615,101 @@
       <c r="E22" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F22" s="30"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
-      <c r="R22" s="34"/>
-      <c r="S22" s="11"/>
-      <c r="T22" s="30"/>
-      <c r="U22" s="11"/>
-      <c r="V22" s="31"/>
-      <c r="W22" s="11"/>
-      <c r="X22" s="11"/>
-      <c r="Y22" s="34"/>
-      <c r="Z22" s="11"/>
-      <c r="AA22" s="30"/>
-      <c r="AB22" s="11"/>
-      <c r="AC22" s="11"/>
-      <c r="AD22" s="11"/>
-      <c r="AE22" s="11"/>
-      <c r="AF22" s="34"/>
-      <c r="AG22" s="11"/>
-      <c r="AH22" s="11"/>
-      <c r="AI22" s="30"/>
-      <c r="AJ22" s="11"/>
+      <c r="F22" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G22" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H22" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I22" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J22" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="K22" s="25"/>
+      <c r="L22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R22" s="25"/>
+      <c r="S22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W22" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="X22" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y22" s="25"/>
+      <c r="Z22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA22" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF22" s="25"/>
+      <c r="AG22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI22" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AJ22" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK22" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL22" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>19</v>
       </c>
@@ -2695,47 +3723,101 @@
       <c r="E23" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="30"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
-      <c r="R23" s="34"/>
-      <c r="S23" s="11"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="11"/>
-      <c r="V23" s="31"/>
-      <c r="W23" s="11"/>
-      <c r="X23" s="11"/>
-      <c r="Y23" s="34"/>
-      <c r="Z23" s="11"/>
-      <c r="AA23" s="30"/>
-      <c r="AB23" s="11"/>
-      <c r="AC23" s="11"/>
-      <c r="AD23" s="11"/>
-      <c r="AE23" s="11"/>
-      <c r="AF23" s="34"/>
-      <c r="AG23" s="11"/>
-      <c r="AH23" s="11"/>
-      <c r="AI23" s="30"/>
-      <c r="AJ23" s="11"/>
+      <c r="F23" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H23" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I23" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J23" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="K23" s="25"/>
+      <c r="L23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q23" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="R23" s="25"/>
+      <c r="S23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y23" s="25"/>
+      <c r="Z23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE23" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF23" s="25"/>
+      <c r="AG23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ23" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK23" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL23" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A24" s="12">
         <v>20</v>
       </c>
@@ -2749,47 +3831,101 @@
       <c r="E24" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="30"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
-      <c r="R24" s="34"/>
-      <c r="S24" s="11"/>
-      <c r="T24" s="30"/>
-      <c r="U24" s="11"/>
-      <c r="V24" s="31"/>
-      <c r="W24" s="11"/>
-      <c r="X24" s="11"/>
-      <c r="Y24" s="34"/>
-      <c r="Z24" s="11"/>
-      <c r="AA24" s="30"/>
-      <c r="AB24" s="11"/>
-      <c r="AC24" s="11"/>
-      <c r="AD24" s="11"/>
-      <c r="AE24" s="11"/>
-      <c r="AF24" s="34"/>
-      <c r="AG24" s="11"/>
-      <c r="AH24" s="11"/>
-      <c r="AI24" s="30"/>
-      <c r="AJ24" s="11"/>
+      <c r="F24" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H24" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I24" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J24" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="K24" s="25"/>
+      <c r="L24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R24" s="25"/>
+      <c r="S24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X24" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y24" s="25"/>
+      <c r="Z24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF24" s="25"/>
+      <c r="AG24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ24" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK24" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL24" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>21</v>
       </c>
@@ -2803,47 +3939,101 @@
       <c r="E25" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="30"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="34"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
-      <c r="R25" s="34"/>
-      <c r="S25" s="11"/>
-      <c r="T25" s="30"/>
-      <c r="U25" s="11"/>
-      <c r="V25" s="31"/>
-      <c r="W25" s="11"/>
-      <c r="X25" s="11"/>
-      <c r="Y25" s="34"/>
-      <c r="Z25" s="11"/>
-      <c r="AA25" s="30"/>
-      <c r="AB25" s="11"/>
-      <c r="AC25" s="11"/>
-      <c r="AD25" s="11"/>
-      <c r="AE25" s="11"/>
-      <c r="AF25" s="34"/>
-      <c r="AG25" s="11"/>
-      <c r="AH25" s="11"/>
-      <c r="AI25" s="30"/>
-      <c r="AJ25" s="11"/>
+      <c r="F25" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G25" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H25" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I25" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J25" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="K25" s="25"/>
+      <c r="L25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q25" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="R25" s="25"/>
+      <c r="S25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y25" s="25"/>
+      <c r="Z25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF25" s="25"/>
+      <c r="AG25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ25" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK25" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL25" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A26" s="12">
         <v>22</v>
       </c>
@@ -2857,47 +4047,101 @@
       <c r="E26" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F26" s="30"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="34"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="11"/>
-      <c r="R26" s="34"/>
-      <c r="S26" s="11"/>
-      <c r="T26" s="30"/>
-      <c r="U26" s="11"/>
-      <c r="V26" s="31"/>
-      <c r="W26" s="11"/>
-      <c r="X26" s="11"/>
-      <c r="Y26" s="34"/>
-      <c r="Z26" s="11"/>
-      <c r="AA26" s="30"/>
-      <c r="AB26" s="11"/>
-      <c r="AC26" s="11"/>
-      <c r="AD26" s="11"/>
-      <c r="AE26" s="11"/>
-      <c r="AF26" s="34"/>
-      <c r="AG26" s="11"/>
-      <c r="AH26" s="11"/>
-      <c r="AI26" s="30"/>
-      <c r="AJ26" s="11"/>
+      <c r="F26" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="H26" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I26" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J26" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="K26" s="25"/>
+      <c r="L26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R26" s="25"/>
+      <c r="S26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W26" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="X26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y26" s="25"/>
+      <c r="Z26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE26" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF26" s="25"/>
+      <c r="AG26" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ26" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK26" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL26" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>23</v>
       </c>
@@ -2911,47 +4155,101 @@
       <c r="E27" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F27" s="30"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="34"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="30"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="11"/>
-      <c r="Q27" s="11"/>
-      <c r="R27" s="34"/>
-      <c r="S27" s="11"/>
-      <c r="T27" s="30"/>
-      <c r="U27" s="11"/>
-      <c r="V27" s="31"/>
-      <c r="W27" s="11"/>
-      <c r="X27" s="11"/>
-      <c r="Y27" s="34"/>
-      <c r="Z27" s="11"/>
-      <c r="AA27" s="30"/>
-      <c r="AB27" s="11"/>
-      <c r="AC27" s="11"/>
-      <c r="AD27" s="11"/>
-      <c r="AE27" s="11"/>
-      <c r="AF27" s="34"/>
-      <c r="AG27" s="11"/>
-      <c r="AH27" s="11"/>
-      <c r="AI27" s="30"/>
-      <c r="AJ27" s="11"/>
+      <c r="F27" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H27" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I27" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J27" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="K27" s="25"/>
+      <c r="L27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R27" s="25"/>
+      <c r="S27" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="T27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W27" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="X27" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y27" s="25"/>
+      <c r="Z27" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF27" s="25"/>
+      <c r="AG27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ27" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK27" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL27" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A28" s="12">
         <v>24</v>
       </c>
@@ -2965,56 +4263,107 @@
       <c r="E28" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F28" s="30"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="35"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="30"/>
-      <c r="N28" s="11"/>
-      <c r="O28" s="11"/>
-      <c r="P28" s="11"/>
-      <c r="Q28" s="11"/>
-      <c r="R28" s="35"/>
-      <c r="S28" s="11"/>
-      <c r="T28" s="30"/>
-      <c r="U28" s="11"/>
-      <c r="V28" s="31"/>
-      <c r="W28" s="11"/>
-      <c r="X28" s="11"/>
-      <c r="Y28" s="35"/>
-      <c r="Z28" s="11"/>
-      <c r="AA28" s="30"/>
-      <c r="AB28" s="11"/>
-      <c r="AC28" s="11"/>
-      <c r="AD28" s="11"/>
-      <c r="AE28" s="11"/>
-      <c r="AF28" s="35"/>
-      <c r="AG28" s="11"/>
-      <c r="AH28" s="11"/>
-      <c r="AI28" s="30"/>
-      <c r="AJ28" s="11"/>
+      <c r="F28" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G28" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H28" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I28" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J28" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="K28" s="26"/>
+      <c r="L28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N28" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="O28" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="P28" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q28" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R28" s="26"/>
+      <c r="S28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y28" s="26"/>
+      <c r="Z28" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC28" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD28" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE28" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF28" s="26"/>
+      <c r="AG28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ28" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK28" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL28" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="K29" s="32"/>
+      <c r="K29" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="K5:K28"/>
-    <mergeCell ref="R5:R28"/>
-    <mergeCell ref="Y5:Y28"/>
-    <mergeCell ref="AF5:AF28"/>
-    <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="A2:AJ2"/>
+    <mergeCell ref="A1:AJ1"/>
     <mergeCell ref="AL3:AL4"/>
     <mergeCell ref="AM3:AN3"/>
     <mergeCell ref="AM8:AP8"/>
@@ -3024,58 +4373,82 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="A2:AJ2"/>
-    <mergeCell ref="A1:AJ1"/>
+    <mergeCell ref="K5:K28"/>
+    <mergeCell ref="R5:R28"/>
+    <mergeCell ref="Y5:Y28"/>
+    <mergeCell ref="AF5:AF28"/>
+    <mergeCell ref="AK3:AK4"/>
   </mergeCells>
-  <conditionalFormatting sqref="T5 V5 AA5 AI5 F5:M5 N5:Q28 U5:U28 W5:X28 AB5:AE28 AJ5:AJ28 F4:AJ4 G6:J28 L6:L28 S5:S28 R5 Z5:Z28 Y5 AG5:AH28 AF5">
-    <cfRule type="expression" dxfId="16" priority="14">
+  <conditionalFormatting sqref="F6:I28 L6:Q28 S6:X28 Z6:AE28 F4:AJ5 AG6:AJ28">
+    <cfRule type="expression" dxfId="21" priority="19">
       <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T5 V5 AA5 AI5 F5:M5 N5:Q28 U5:U28 W5:X28 AB5:AE28 AJ5:AJ28 G6:J28 L6:L28 S5:S28 R5 Z5:Z28 Y5 AG5:AH28 AF5">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+  <conditionalFormatting sqref="F6:I28 L6:Q28 S6:X28 Z6:AE28 F5:AJ5 AG6:AJ28">
+    <cfRule type="cellIs" dxfId="20" priority="6" operator="equal">
       <formula>"L"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="7" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="8" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T5 V5 AA5 AI5 F5:M5 N5:Q28 U5:U28 W5:X28 AM4:AN4 AB5:AE28 AJ5:AJ28 G6:J28 L6:L28 S5:S28 R5 Z5:Z28 Y5 AG5:AH28 AF5 F3:AJ4">
-    <cfRule type="expression" dxfId="12" priority="15">
+  <conditionalFormatting sqref="AM4:AN4 F6:I28 L6:Q28 S6:X28 Z6:AE28 F3:AJ5 AG6:AJ28">
+    <cfRule type="expression" dxfId="17" priority="20">
       <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK3:AL3 AK5:AL28">
-    <cfRule type="expression" dxfId="11" priority="16">
+    <cfRule type="expression" dxfId="16" priority="21">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM5:AM6">
-    <cfRule type="expression" dxfId="10" priority="12">
+    <cfRule type="expression" dxfId="15" priority="17">
       <formula>AM$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM9:AM12">
-    <cfRule type="expression" dxfId="9" priority="6">
+    <cfRule type="expression" dxfId="14" priority="11">
       <formula>AM$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM17:AM20">
-    <cfRule type="expression" dxfId="8" priority="5">
+    <cfRule type="expression" dxfId="13" priority="10">
       <formula>AM$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN9:AP9">
-    <cfRule type="expression" dxfId="7" priority="7">
+    <cfRule type="expression" dxfId="12" priority="12">
       <formula>AN$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN17:AP17">
-    <cfRule type="expression" dxfId="6" priority="4">
+    <cfRule type="expression" dxfId="11" priority="9">
       <formula>AN$3="Sun"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6:J28">
+    <cfRule type="expression" dxfId="10" priority="4">
+      <formula>IF(J$4=TODAY(),TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6:J28">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+      <formula>"L"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+      <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J6:J28">
+    <cfRule type="expression" dxfId="6" priority="5">
+      <formula>J$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3132,99 +4505,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
-      <c r="V1" s="22"/>
-      <c r="W1" s="22"/>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="22"/>
-      <c r="AB1" s="22"/>
-      <c r="AC1" s="22"/>
-      <c r="AD1" s="22"/>
-      <c r="AE1" s="22"/>
-      <c r="AF1" s="22"/>
-      <c r="AG1" s="22"/>
-      <c r="AH1" s="22"/>
-      <c r="AI1" s="22"/>
-      <c r="AJ1" s="22"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="34"/>
+      <c r="AD1" s="34"/>
+      <c r="AE1" s="34"/>
+      <c r="AF1" s="34"/>
+      <c r="AG1" s="34"/>
+      <c r="AH1" s="34"/>
+      <c r="AI1" s="34"/>
+      <c r="AJ1" s="34"/>
     </row>
     <row r="2" spans="1:42" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="29"/>
-      <c r="AB2" s="29"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="29"/>
-      <c r="AE2" s="29"/>
-      <c r="AF2" s="29"/>
-      <c r="AG2" s="29"/>
-      <c r="AH2" s="29"/>
-      <c r="AI2" s="29"/>
-      <c r="AJ2" s="29"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
+      <c r="T2" s="33"/>
+      <c r="U2" s="33"/>
+      <c r="V2" s="33"/>
+      <c r="W2" s="33"/>
+      <c r="X2" s="33"/>
+      <c r="Y2" s="33"/>
+      <c r="Z2" s="33"/>
+      <c r="AA2" s="33"/>
+      <c r="AB2" s="33"/>
+      <c r="AC2" s="33"/>
+      <c r="AD2" s="33"/>
+      <c r="AE2" s="33"/>
+      <c r="AF2" s="33"/>
+      <c r="AG2" s="33"/>
+      <c r="AH2" s="33"/>
+      <c r="AI2" s="33"/>
+      <c r="AJ2" s="33"/>
     </row>
     <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="31" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -3351,25 +4724,25 @@
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="AK3" s="25" t="s">
+      <c r="AK3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="AL3" s="25" t="s">
+      <c r="AL3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="AM3" s="26" t="s">
+      <c r="AM3" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="AN3" s="27"/>
+      <c r="AN3" s="29"/>
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
     </row>
     <row r="4" spans="1:42" ht="34.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="24"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
       <c r="F4" s="21">
         <v>45566</v>
       </c>
@@ -3463,8 +4836,8 @@
       <c r="AJ4" s="21">
         <v>45596</v>
       </c>
-      <c r="AK4" s="25"/>
-      <c r="AL4" s="25"/>
+      <c r="AK4" s="27"/>
+      <c r="AL4" s="27"/>
       <c r="AM4" s="4" t="s">
         <v>7</v>
       </c>
@@ -3488,52 +4861,106 @@
       <c r="E5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="30"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="33" t="s">
+      <c r="F5" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H5" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I5" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="K5" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="L5" s="11"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
-      <c r="R5" s="33" t="s">
+      <c r="L5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R5" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="S5" s="11"/>
-      <c r="T5" s="30"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="31"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="33" t="s">
+      <c r="S5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X5" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y5" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="Z5" s="11"/>
-      <c r="AA5" s="30"/>
-      <c r="AB5" s="11"/>
-      <c r="AC5" s="11"/>
-      <c r="AD5" s="11"/>
-      <c r="AE5" s="11"/>
-      <c r="AF5" s="33" t="s">
+      <c r="Z5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE5" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF5" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="AG5" s="11"/>
-      <c r="AH5" s="11"/>
-      <c r="AI5" s="30"/>
-      <c r="AJ5" s="11"/>
+      <c r="AG5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ5" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK5" s="5">
         <f t="shared" ref="AK5:AK36" si="1">COUNTIF(F5:AJ5,"P")</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL5" s="5">
         <f t="shared" ref="AL5:AL36" si="2">COUNTIF(F5:AJ5,"A")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM5" s="5" t="s">
         <v>8</v>
@@ -3546,7 +4973,7 @@
       </c>
       <c r="AP5" s="3"/>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -3560,44 +4987,98 @@
       <c r="E6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="30"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="34"/>
-      <c r="S6" s="11"/>
-      <c r="T6" s="30"/>
-      <c r="U6" s="11"/>
-      <c r="V6" s="31"/>
-      <c r="W6" s="11"/>
-      <c r="X6" s="11"/>
-      <c r="Y6" s="34"/>
-      <c r="Z6" s="11"/>
-      <c r="AA6" s="30"/>
-      <c r="AB6" s="11"/>
-      <c r="AC6" s="11"/>
-      <c r="AD6" s="11"/>
-      <c r="AE6" s="11"/>
-      <c r="AF6" s="34"/>
-      <c r="AG6" s="11"/>
-      <c r="AH6" s="11"/>
-      <c r="AI6" s="30"/>
-      <c r="AJ6" s="11"/>
+      <c r="F6" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I6" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="K6" s="25"/>
+      <c r="L6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R6" s="25"/>
+      <c r="S6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W6" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="X6" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y6" s="25"/>
+      <c r="Z6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD6" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF6" s="25"/>
+      <c r="AG6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ6" s="11" t="s">
+        <v>129</v>
+      </c>
       <c r="AK6" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL6" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM6" s="5" t="s">
         <v>10</v>
@@ -3608,7 +5089,7 @@
       <c r="AO6" s="3"/>
       <c r="AP6" s="3"/>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>3</v>
       </c>
@@ -3622,51 +5103,105 @@
       <c r="E7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="30"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
-      <c r="R7" s="34"/>
-      <c r="S7" s="11"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="11"/>
-      <c r="V7" s="31"/>
-      <c r="W7" s="11"/>
-      <c r="X7" s="11"/>
-      <c r="Y7" s="34"/>
-      <c r="Z7" s="11"/>
-      <c r="AA7" s="30"/>
-      <c r="AB7" s="11"/>
-      <c r="AC7" s="11"/>
-      <c r="AD7" s="11"/>
-      <c r="AE7" s="11"/>
-      <c r="AF7" s="34"/>
-      <c r="AG7" s="11"/>
-      <c r="AH7" s="11"/>
-      <c r="AI7" s="30"/>
-      <c r="AJ7" s="11"/>
+      <c r="F7" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H7" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I7" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J7" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="K7" s="25"/>
+      <c r="L7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R7" s="25"/>
+      <c r="S7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y7" s="25"/>
+      <c r="Z7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA7" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB7" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AC7" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD7" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF7" s="25"/>
+      <c r="AG7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ7" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK7" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL7" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM7" s="3"/>
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
       <c r="AP7" s="3"/>
     </row>
-    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -3680,53 +5215,107 @@
       <c r="E8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="30"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="34"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="30"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="31"/>
-      <c r="W8" s="11"/>
-      <c r="X8" s="11"/>
-      <c r="Y8" s="34"/>
-      <c r="Z8" s="11"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="11"/>
-      <c r="AC8" s="11"/>
-      <c r="AD8" s="11"/>
-      <c r="AE8" s="11"/>
-      <c r="AF8" s="34"/>
-      <c r="AG8" s="11"/>
-      <c r="AH8" s="11"/>
-      <c r="AI8" s="30"/>
-      <c r="AJ8" s="11"/>
+      <c r="F8" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="I8" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="K8" s="25"/>
+      <c r="L8" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q8" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="R8" s="25"/>
+      <c r="S8" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="T8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W8" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="X8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y8" s="25"/>
+      <c r="Z8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD8" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF8" s="25"/>
+      <c r="AG8" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH8" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI8" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AJ8" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK8" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL8" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AM8" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM8" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="AN8" s="27"/>
-      <c r="AO8" s="27"/>
-      <c r="AP8" s="28"/>
+      <c r="AN8" s="29"/>
+      <c r="AO8" s="29"/>
+      <c r="AP8" s="30"/>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>5</v>
       </c>
@@ -3740,44 +5329,98 @@
       <c r="E9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="30"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="34"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="30"/>
-      <c r="U9" s="11"/>
-      <c r="V9" s="31"/>
-      <c r="W9" s="11"/>
-      <c r="X9" s="11"/>
-      <c r="Y9" s="34"/>
-      <c r="Z9" s="11"/>
-      <c r="AA9" s="30"/>
-      <c r="AB9" s="11"/>
-      <c r="AC9" s="11"/>
-      <c r="AD9" s="11"/>
-      <c r="AE9" s="11"/>
-      <c r="AF9" s="34"/>
-      <c r="AG9" s="11"/>
-      <c r="AH9" s="11"/>
-      <c r="AI9" s="30"/>
-      <c r="AJ9" s="11"/>
+      <c r="F9" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I9" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J9" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="K9" s="25"/>
+      <c r="L9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R9" s="25"/>
+      <c r="S9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y9" s="25"/>
+      <c r="Z9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE9" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF9" s="25"/>
+      <c r="AG9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ9" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK9" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL9" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM9" s="5" t="s">
         <v>12</v>
@@ -3792,7 +5435,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>6</v>
       </c>
@@ -3806,44 +5449,98 @@
       <c r="E10" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="30"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="34"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="30"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="31"/>
-      <c r="W10" s="11"/>
-      <c r="X10" s="11"/>
-      <c r="Y10" s="34"/>
-      <c r="Z10" s="11"/>
-      <c r="AA10" s="30"/>
-      <c r="AB10" s="11"/>
-      <c r="AC10" s="11"/>
-      <c r="AD10" s="11"/>
-      <c r="AE10" s="11"/>
-      <c r="AF10" s="34"/>
-      <c r="AG10" s="11"/>
-      <c r="AH10" s="11"/>
-      <c r="AI10" s="30"/>
-      <c r="AJ10" s="11"/>
+      <c r="F10" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H10" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="K10" s="25"/>
+      <c r="L10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R10" s="25"/>
+      <c r="S10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y10" s="25"/>
+      <c r="Z10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF10" s="25"/>
+      <c r="AG10" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH10" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI10" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ10" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK10" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL10" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM10" s="5" t="s">
         <v>16</v>
@@ -3861,7 +5558,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>7</v>
       </c>
@@ -3875,62 +5572,116 @@
       <c r="E11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="30"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="34"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="30"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="31"/>
-      <c r="W11" s="11"/>
-      <c r="X11" s="11"/>
-      <c r="Y11" s="34"/>
-      <c r="Z11" s="11"/>
-      <c r="AA11" s="30"/>
-      <c r="AB11" s="11"/>
-      <c r="AC11" s="11"/>
-      <c r="AD11" s="11"/>
-      <c r="AE11" s="11"/>
-      <c r="AF11" s="34"/>
-      <c r="AG11" s="11"/>
-      <c r="AH11" s="11"/>
-      <c r="AI11" s="30"/>
-      <c r="AJ11" s="11"/>
+      <c r="F11" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I11" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="K11" s="25"/>
+      <c r="L11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q11" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="R11" s="25"/>
+      <c r="S11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y11" s="25"/>
+      <c r="Z11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF11" s="25"/>
+      <c r="AG11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ11" s="11" t="s">
+        <v>129</v>
+      </c>
       <c r="AK11" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL11" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM11" s="5" t="s">
         <v>17</v>
       </c>
       <c r="AN11" s="12">
         <f>+AK7+AK18</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AO11" s="12">
         <f>AK5+AK6+AK8+AK9+AK10+AK11+AK12+AK13+AK14+AK15+AK16+AK17+AK19+AK20</f>
-        <v>0</v>
+        <v>331</v>
       </c>
       <c r="AP11" s="12">
         <f>AN11+AO11</f>
-        <v>0</v>
+        <v>379</v>
       </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="12">
         <v>8</v>
       </c>
@@ -3944,62 +5695,116 @@
       <c r="E12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="30"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="34"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="30"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="31"/>
-      <c r="W12" s="11"/>
-      <c r="X12" s="11"/>
-      <c r="Y12" s="34"/>
-      <c r="Z12" s="11"/>
-      <c r="AA12" s="30"/>
-      <c r="AB12" s="11"/>
-      <c r="AC12" s="11"/>
-      <c r="AD12" s="11"/>
-      <c r="AE12" s="11"/>
-      <c r="AF12" s="34"/>
-      <c r="AG12" s="11"/>
-      <c r="AH12" s="11"/>
-      <c r="AI12" s="30"/>
-      <c r="AJ12" s="11"/>
+      <c r="F12" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I12" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J12" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="K12" s="25"/>
+      <c r="L12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R12" s="25"/>
+      <c r="S12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="T12" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="U12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y12" s="25"/>
+      <c r="Z12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC12" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF12" s="25"/>
+      <c r="AG12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI12" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ12" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK12" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL12" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM12" s="5" t="s">
         <v>18</v>
       </c>
       <c r="AN12" s="12">
         <f>AN11/AN10</f>
-        <v>0</v>
+        <v>9.7165991902834009E-2</v>
       </c>
       <c r="AO12" s="12">
         <f>AO11/AO10</f>
-        <v>0</v>
+        <v>0.60622710622710618</v>
       </c>
       <c r="AP12" s="12">
         <f>AP11/AP10</f>
-        <v>0</v>
+        <v>0.36442307692307691</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>9</v>
       </c>
@@ -4013,40 +5818,94 @@
       <c r="E13" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="30"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="34"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="30"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="31"/>
-      <c r="W13" s="11"/>
-      <c r="X13" s="11"/>
-      <c r="Y13" s="34"/>
-      <c r="Z13" s="11"/>
-      <c r="AA13" s="30"/>
-      <c r="AB13" s="11"/>
-      <c r="AC13" s="11"/>
-      <c r="AD13" s="11"/>
-      <c r="AE13" s="11"/>
-      <c r="AF13" s="34"/>
-      <c r="AG13" s="11"/>
-      <c r="AH13" s="11"/>
-      <c r="AI13" s="30"/>
-      <c r="AJ13" s="11"/>
+      <c r="F13" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H13" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="K13" s="25"/>
+      <c r="L13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R13" s="25"/>
+      <c r="S13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y13" s="25"/>
+      <c r="Z13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF13" s="25"/>
+      <c r="AG13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI13" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ13" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK13" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL13" s="5">
         <f t="shared" si="2"/>
@@ -4057,7 +5916,7 @@
       <c r="AO13" s="17"/>
       <c r="AP13" s="17"/>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="12">
         <v>10</v>
       </c>
@@ -4071,40 +5930,94 @@
       <c r="E14" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="30"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="34"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="30"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="31"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="11"/>
-      <c r="Y14" s="34"/>
-      <c r="Z14" s="11"/>
-      <c r="AA14" s="30"/>
-      <c r="AB14" s="11"/>
-      <c r="AC14" s="11"/>
-      <c r="AD14" s="11"/>
-      <c r="AE14" s="11"/>
-      <c r="AF14" s="34"/>
-      <c r="AG14" s="11"/>
-      <c r="AH14" s="11"/>
-      <c r="AI14" s="30"/>
-      <c r="AJ14" s="11"/>
+      <c r="F14" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I14" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J14" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="K14" s="25"/>
+      <c r="L14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R14" s="25"/>
+      <c r="S14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y14" s="25"/>
+      <c r="Z14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF14" s="25"/>
+      <c r="AG14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI14" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ14" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK14" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL14" s="5">
         <f t="shared" si="2"/>
@@ -4115,7 +6028,7 @@
       <c r="AO14" s="19"/>
       <c r="AP14" s="19"/>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>11</v>
       </c>
@@ -4129,51 +6042,105 @@
       <c r="E15" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="30"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="11"/>
-      <c r="T15" s="30"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="31"/>
-      <c r="W15" s="11"/>
-      <c r="X15" s="11"/>
-      <c r="Y15" s="34"/>
-      <c r="Z15" s="11"/>
-      <c r="AA15" s="30"/>
-      <c r="AB15" s="11"/>
-      <c r="AC15" s="11"/>
-      <c r="AD15" s="11"/>
-      <c r="AE15" s="11"/>
-      <c r="AF15" s="34"/>
-      <c r="AG15" s="11"/>
-      <c r="AH15" s="11"/>
-      <c r="AI15" s="30"/>
-      <c r="AJ15" s="11"/>
+      <c r="F15" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H15" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I15" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="J15" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="K15" s="25"/>
+      <c r="L15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="N15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R15" s="25"/>
+      <c r="S15" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="T15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X15" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y15" s="25"/>
+      <c r="Z15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE15" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF15" s="25"/>
+      <c r="AG15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI15" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ15" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK15" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL15" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM15" s="3"/>
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
     </row>
-    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="12">
         <v>12</v>
       </c>
@@ -4187,53 +6154,107 @@
       <c r="E16" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="30"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="34"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="30"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="31"/>
-      <c r="W16" s="11"/>
-      <c r="X16" s="11"/>
-      <c r="Y16" s="34"/>
-      <c r="Z16" s="11"/>
-      <c r="AA16" s="30"/>
-      <c r="AB16" s="11"/>
-      <c r="AC16" s="11"/>
-      <c r="AD16" s="11"/>
-      <c r="AE16" s="11"/>
-      <c r="AF16" s="34"/>
-      <c r="AG16" s="11"/>
-      <c r="AH16" s="11"/>
-      <c r="AI16" s="30"/>
-      <c r="AJ16" s="11"/>
+      <c r="F16" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I16" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="K16" s="25"/>
+      <c r="L16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R16" s="25"/>
+      <c r="S16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y16" s="25"/>
+      <c r="Z16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF16" s="25"/>
+      <c r="AG16" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH16" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI16" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AJ16" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK16" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL16" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AM16" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM16" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="AN16" s="27"/>
-      <c r="AO16" s="27"/>
-      <c r="AP16" s="28"/>
+      <c r="AN16" s="29"/>
+      <c r="AO16" s="29"/>
+      <c r="AP16" s="30"/>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>13</v>
       </c>
@@ -4247,40 +6268,94 @@
       <c r="E17" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="30"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="34"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="30"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="31"/>
-      <c r="W17" s="11"/>
-      <c r="X17" s="11"/>
-      <c r="Y17" s="34"/>
-      <c r="Z17" s="11"/>
-      <c r="AA17" s="30"/>
-      <c r="AB17" s="11"/>
-      <c r="AC17" s="11"/>
-      <c r="AD17" s="11"/>
-      <c r="AE17" s="11"/>
-      <c r="AF17" s="34"/>
-      <c r="AG17" s="11"/>
-      <c r="AH17" s="11"/>
-      <c r="AI17" s="30"/>
-      <c r="AJ17" s="11"/>
+      <c r="F17" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H17" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I17" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="K17" s="25"/>
+      <c r="L17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O17" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="P17" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R17" s="25"/>
+      <c r="S17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y17" s="25"/>
+      <c r="Z17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF17" s="25"/>
+      <c r="AG17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ17" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK17" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL17" s="5">
         <f t="shared" si="2"/>
@@ -4299,7 +6374,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A18" s="12">
         <v>14</v>
       </c>
@@ -4313,40 +6388,94 @@
       <c r="E18" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="30"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="34"/>
-      <c r="S18" s="11"/>
-      <c r="T18" s="30"/>
-      <c r="U18" s="11"/>
-      <c r="V18" s="31"/>
-      <c r="W18" s="11"/>
-      <c r="X18" s="11"/>
-      <c r="Y18" s="34"/>
-      <c r="Z18" s="11"/>
-      <c r="AA18" s="30"/>
-      <c r="AB18" s="11"/>
-      <c r="AC18" s="11"/>
-      <c r="AD18" s="11"/>
-      <c r="AE18" s="11"/>
-      <c r="AF18" s="34"/>
-      <c r="AG18" s="11"/>
-      <c r="AH18" s="11"/>
-      <c r="AI18" s="30"/>
-      <c r="AJ18" s="11"/>
+      <c r="F18" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H18" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I18" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J18" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="K18" s="25"/>
+      <c r="L18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R18" s="25"/>
+      <c r="S18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y18" s="25"/>
+      <c r="Z18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF18" s="25"/>
+      <c r="AG18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ18" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK18" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL18" s="5">
         <f t="shared" si="2"/>
@@ -4368,7 +6497,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>15</v>
       </c>
@@ -4382,40 +6511,94 @@
       <c r="E19" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="30"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="34"/>
-      <c r="S19" s="11"/>
-      <c r="T19" s="30"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="31"/>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11"/>
-      <c r="Y19" s="34"/>
-      <c r="Z19" s="11"/>
-      <c r="AA19" s="30"/>
-      <c r="AB19" s="11"/>
-      <c r="AC19" s="11"/>
-      <c r="AD19" s="11"/>
-      <c r="AE19" s="11"/>
-      <c r="AF19" s="34"/>
-      <c r="AG19" s="11"/>
-      <c r="AH19" s="11"/>
-      <c r="AI19" s="30"/>
-      <c r="AJ19" s="11"/>
+      <c r="F19" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H19" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I19" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="K19" s="25"/>
+      <c r="L19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R19" s="25"/>
+      <c r="S19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y19" s="25"/>
+      <c r="Z19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF19" s="25"/>
+      <c r="AG19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ19" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK19" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL19" s="5">
         <f t="shared" si="2"/>
@@ -4426,18 +6609,18 @@
       </c>
       <c r="AN19" s="12">
         <f>AN18-AN11</f>
-        <v>494</v>
+        <v>446</v>
       </c>
       <c r="AO19" s="12">
         <f>AO18-AO11</f>
-        <v>546</v>
+        <v>215</v>
       </c>
       <c r="AP19" s="12">
         <f>AN19+AO19</f>
-        <v>1040</v>
+        <v>661</v>
       </c>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A20" s="12">
         <v>16</v>
       </c>
@@ -4451,62 +6634,116 @@
       <c r="E20" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F20" s="30"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="34"/>
-      <c r="S20" s="11"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="11"/>
-      <c r="V20" s="31"/>
-      <c r="W20" s="11"/>
-      <c r="X20" s="11"/>
-      <c r="Y20" s="34"/>
-      <c r="Z20" s="11"/>
-      <c r="AA20" s="30"/>
-      <c r="AB20" s="11"/>
-      <c r="AC20" s="11"/>
-      <c r="AD20" s="11"/>
-      <c r="AE20" s="11"/>
-      <c r="AF20" s="34"/>
-      <c r="AG20" s="11"/>
-      <c r="AH20" s="11"/>
-      <c r="AI20" s="30"/>
-      <c r="AJ20" s="11"/>
+      <c r="F20" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H20" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I20" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J20" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="K20" s="25"/>
+      <c r="L20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="N20" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="O20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R20" s="25"/>
+      <c r="S20" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="T20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y20" s="25"/>
+      <c r="Z20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC20" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF20" s="25"/>
+      <c r="AG20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ20" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK20" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL20" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM20" s="5" t="s">
         <v>15</v>
       </c>
       <c r="AN20" s="20">
         <f>AN19/AN18</f>
-        <v>1</v>
+        <v>0.90283400809716596</v>
       </c>
       <c r="AO20" s="20">
         <f>AO19/AO18</f>
-        <v>1</v>
+        <v>0.39377289377289376</v>
       </c>
       <c r="AP20" s="20">
         <f>AP19/AP18</f>
-        <v>1</v>
+        <v>0.63557692307692304</v>
       </c>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>17</v>
       </c>
@@ -4520,47 +6757,101 @@
       <c r="E21" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="30"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-      <c r="Q21" s="11"/>
-      <c r="R21" s="34"/>
-      <c r="S21" s="11"/>
-      <c r="T21" s="30"/>
-      <c r="U21" s="11"/>
-      <c r="V21" s="31"/>
-      <c r="W21" s="11"/>
-      <c r="X21" s="11"/>
-      <c r="Y21" s="34"/>
-      <c r="Z21" s="11"/>
-      <c r="AA21" s="30"/>
-      <c r="AB21" s="11"/>
-      <c r="AC21" s="11"/>
-      <c r="AD21" s="11"/>
-      <c r="AE21" s="11"/>
-      <c r="AF21" s="34"/>
-      <c r="AG21" s="11"/>
-      <c r="AH21" s="11"/>
-      <c r="AI21" s="30"/>
-      <c r="AJ21" s="11"/>
+      <c r="F21" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H21" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="I21" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J21" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="K21" s="25"/>
+      <c r="L21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q21" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="R21" s="25"/>
+      <c r="S21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y21" s="25"/>
+      <c r="Z21" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD21" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF21" s="25"/>
+      <c r="AG21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ21" s="11" t="s">
+        <v>129</v>
+      </c>
       <c r="AK21" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL21" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A22" s="12">
         <v>18</v>
       </c>
@@ -4574,47 +6865,101 @@
       <c r="E22" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F22" s="30"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
-      <c r="R22" s="34"/>
-      <c r="S22" s="11"/>
-      <c r="T22" s="30"/>
-      <c r="U22" s="11"/>
-      <c r="V22" s="31"/>
-      <c r="W22" s="11"/>
-      <c r="X22" s="11"/>
-      <c r="Y22" s="34"/>
-      <c r="Z22" s="11"/>
-      <c r="AA22" s="30"/>
-      <c r="AB22" s="11"/>
-      <c r="AC22" s="11"/>
-      <c r="AD22" s="11"/>
-      <c r="AE22" s="11"/>
-      <c r="AF22" s="34"/>
-      <c r="AG22" s="11"/>
-      <c r="AH22" s="11"/>
-      <c r="AI22" s="30"/>
-      <c r="AJ22" s="11"/>
+      <c r="F22" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G22" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H22" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I22" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="K22" s="25"/>
+      <c r="L22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R22" s="25"/>
+      <c r="S22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y22" s="25"/>
+      <c r="Z22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF22" s="25"/>
+      <c r="AG22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ22" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK22" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL22" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>19</v>
       </c>
@@ -4628,47 +6973,101 @@
       <c r="E23" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="30"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
-      <c r="R23" s="34"/>
-      <c r="S23" s="11"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="11"/>
-      <c r="V23" s="31"/>
-      <c r="W23" s="11"/>
-      <c r="X23" s="11"/>
-      <c r="Y23" s="34"/>
-      <c r="Z23" s="11"/>
-      <c r="AA23" s="30"/>
-      <c r="AB23" s="11"/>
-      <c r="AC23" s="11"/>
-      <c r="AD23" s="11"/>
-      <c r="AE23" s="11"/>
-      <c r="AF23" s="34"/>
-      <c r="AG23" s="11"/>
-      <c r="AH23" s="11"/>
-      <c r="AI23" s="30"/>
-      <c r="AJ23" s="11"/>
+      <c r="F23" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H23" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I23" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="K23" s="25"/>
+      <c r="L23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R23" s="25"/>
+      <c r="S23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y23" s="25"/>
+      <c r="Z23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF23" s="25"/>
+      <c r="AG23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI23" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ23" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK23" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL23" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A24" s="12">
         <v>20</v>
       </c>
@@ -4682,47 +7081,101 @@
       <c r="E24" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="30"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
-      <c r="R24" s="34"/>
-      <c r="S24" s="11"/>
-      <c r="T24" s="30"/>
-      <c r="U24" s="11"/>
-      <c r="V24" s="31"/>
-      <c r="W24" s="11"/>
-      <c r="X24" s="11"/>
-      <c r="Y24" s="34"/>
-      <c r="Z24" s="11"/>
-      <c r="AA24" s="30"/>
-      <c r="AB24" s="11"/>
-      <c r="AC24" s="11"/>
-      <c r="AD24" s="11"/>
-      <c r="AE24" s="11"/>
-      <c r="AF24" s="34"/>
-      <c r="AG24" s="11"/>
-      <c r="AH24" s="11"/>
-      <c r="AI24" s="30"/>
-      <c r="AJ24" s="11"/>
+      <c r="F24" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H24" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I24" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="K24" s="25"/>
+      <c r="L24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R24" s="25"/>
+      <c r="S24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y24" s="25"/>
+      <c r="Z24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF24" s="25"/>
+      <c r="AG24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ24" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK24" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL24" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>21</v>
       </c>
@@ -4736,47 +7189,101 @@
       <c r="E25" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="30"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="34"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="30"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
-      <c r="R25" s="34"/>
-      <c r="S25" s="11"/>
-      <c r="T25" s="30"/>
-      <c r="U25" s="11"/>
-      <c r="V25" s="31"/>
-      <c r="W25" s="11"/>
-      <c r="X25" s="11"/>
-      <c r="Y25" s="34"/>
-      <c r="Z25" s="11"/>
-      <c r="AA25" s="30"/>
-      <c r="AB25" s="11"/>
-      <c r="AC25" s="11"/>
-      <c r="AD25" s="11"/>
-      <c r="AE25" s="11"/>
-      <c r="AF25" s="34"/>
-      <c r="AG25" s="11"/>
-      <c r="AH25" s="11"/>
-      <c r="AI25" s="30"/>
-      <c r="AJ25" s="11"/>
+      <c r="F25" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G25" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H25" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I25" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J25" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="K25" s="25"/>
+      <c r="L25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R25" s="25"/>
+      <c r="S25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W25" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="X25" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y25" s="25"/>
+      <c r="Z25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF25" s="25"/>
+      <c r="AG25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI25" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ25" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK25" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL25" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A26" s="12">
         <v>22</v>
       </c>
@@ -4790,47 +7297,101 @@
       <c r="E26" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F26" s="30"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="34"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="11"/>
-      <c r="R26" s="34"/>
-      <c r="S26" s="11"/>
-      <c r="T26" s="30"/>
-      <c r="U26" s="11"/>
-      <c r="V26" s="31"/>
-      <c r="W26" s="11"/>
-      <c r="X26" s="11"/>
-      <c r="Y26" s="34"/>
-      <c r="Z26" s="11"/>
-      <c r="AA26" s="30"/>
-      <c r="AB26" s="11"/>
-      <c r="AC26" s="11"/>
-      <c r="AD26" s="11"/>
-      <c r="AE26" s="11"/>
-      <c r="AF26" s="34"/>
-      <c r="AG26" s="11"/>
-      <c r="AH26" s="11"/>
-      <c r="AI26" s="30"/>
-      <c r="AJ26" s="11"/>
+      <c r="F26" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H26" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I26" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="K26" s="25"/>
+      <c r="L26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R26" s="25"/>
+      <c r="S26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T26" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="U26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y26" s="25"/>
+      <c r="Z26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF26" s="25"/>
+      <c r="AG26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ26" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK26" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL26" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>23</v>
       </c>
@@ -4844,47 +7405,101 @@
       <c r="E27" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F27" s="30"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="34"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="30"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="11"/>
-      <c r="Q27" s="11"/>
-      <c r="R27" s="34"/>
-      <c r="S27" s="11"/>
-      <c r="T27" s="30"/>
-      <c r="U27" s="11"/>
-      <c r="V27" s="31"/>
-      <c r="W27" s="11"/>
-      <c r="X27" s="11"/>
-      <c r="Y27" s="34"/>
-      <c r="Z27" s="11"/>
-      <c r="AA27" s="30"/>
-      <c r="AB27" s="11"/>
-      <c r="AC27" s="11"/>
-      <c r="AD27" s="11"/>
-      <c r="AE27" s="11"/>
-      <c r="AF27" s="34"/>
-      <c r="AG27" s="11"/>
-      <c r="AH27" s="11"/>
-      <c r="AI27" s="30"/>
-      <c r="AJ27" s="11"/>
+      <c r="F27" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H27" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I27" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J27" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="K27" s="25"/>
+      <c r="L27" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="N27" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="O27" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="P27" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q27" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R27" s="25"/>
+      <c r="S27" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="T27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X27" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y27" s="25"/>
+      <c r="Z27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF27" s="25"/>
+      <c r="AG27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI27" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ27" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK27" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL27" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A28" s="12">
         <v>24</v>
       </c>
@@ -4898,47 +7513,101 @@
       <c r="E28" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F28" s="30"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="30"/>
-      <c r="N28" s="11"/>
-      <c r="O28" s="11"/>
-      <c r="P28" s="11"/>
-      <c r="Q28" s="11"/>
-      <c r="R28" s="34"/>
-      <c r="S28" s="11"/>
-      <c r="T28" s="30"/>
-      <c r="U28" s="11"/>
-      <c r="V28" s="31"/>
-      <c r="W28" s="11"/>
-      <c r="X28" s="11"/>
-      <c r="Y28" s="34"/>
-      <c r="Z28" s="11"/>
-      <c r="AA28" s="30"/>
-      <c r="AB28" s="11"/>
-      <c r="AC28" s="11"/>
-      <c r="AD28" s="11"/>
-      <c r="AE28" s="11"/>
-      <c r="AF28" s="34"/>
-      <c r="AG28" s="11"/>
-      <c r="AH28" s="11"/>
-      <c r="AI28" s="30"/>
-      <c r="AJ28" s="11"/>
+      <c r="F28" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="G28" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="H28" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="I28" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="J28" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="K28" s="25"/>
+      <c r="L28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R28" s="25"/>
+      <c r="S28" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="T28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y28" s="25"/>
+      <c r="Z28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD28" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF28" s="25"/>
+      <c r="AG28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI28" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ28" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK28" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL28" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>25</v>
       </c>
@@ -4952,47 +7621,101 @@
       <c r="E29" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F29" s="30"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="34"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="11"/>
-      <c r="P29" s="11"/>
-      <c r="Q29" s="11"/>
-      <c r="R29" s="34"/>
-      <c r="S29" s="11"/>
-      <c r="T29" s="30"/>
-      <c r="U29" s="11"/>
-      <c r="V29" s="31"/>
-      <c r="W29" s="11"/>
-      <c r="X29" s="11"/>
-      <c r="Y29" s="34"/>
-      <c r="Z29" s="11"/>
-      <c r="AA29" s="30"/>
-      <c r="AB29" s="11"/>
-      <c r="AC29" s="11"/>
-      <c r="AD29" s="11"/>
-      <c r="AE29" s="11"/>
-      <c r="AF29" s="34"/>
-      <c r="AG29" s="11"/>
-      <c r="AH29" s="11"/>
-      <c r="AI29" s="30"/>
-      <c r="AJ29" s="11"/>
+      <c r="F29" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G29" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H29" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I29" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="K29" s="25"/>
+      <c r="L29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O29" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="P29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R29" s="25"/>
+      <c r="S29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y29" s="25"/>
+      <c r="Z29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE29" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF29" s="25"/>
+      <c r="AG29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH29" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ29" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK29" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>COUNTIF(F29:AJ29,"P")</f>
+        <v>23</v>
       </c>
       <c r="AL29" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>COUNTIF(F29:AJ29,"A")</f>
+        <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A30" s="12">
         <v>26</v>
       </c>
@@ -5006,47 +7729,101 @@
       <c r="E30" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="30"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="34"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="30"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="11"/>
-      <c r="P30" s="11"/>
-      <c r="Q30" s="11"/>
-      <c r="R30" s="34"/>
-      <c r="S30" s="11"/>
-      <c r="T30" s="30"/>
-      <c r="U30" s="11"/>
-      <c r="V30" s="31"/>
-      <c r="W30" s="11"/>
-      <c r="X30" s="11"/>
-      <c r="Y30" s="34"/>
-      <c r="Z30" s="11"/>
-      <c r="AA30" s="30"/>
-      <c r="AB30" s="11"/>
-      <c r="AC30" s="11"/>
-      <c r="AD30" s="11"/>
-      <c r="AE30" s="11"/>
-      <c r="AF30" s="34"/>
-      <c r="AG30" s="11"/>
-      <c r="AH30" s="11"/>
-      <c r="AI30" s="30"/>
-      <c r="AJ30" s="11"/>
+      <c r="F30" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G30" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H30" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I30" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J30" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="K30" s="25"/>
+      <c r="L30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="N30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q30" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="R30" s="25"/>
+      <c r="S30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T30" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="U30" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="V30" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="W30" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="X30" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y30" s="25"/>
+      <c r="Z30" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA30" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF30" s="25"/>
+      <c r="AG30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH30" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI30" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ30" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK30" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AL30" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>27</v>
       </c>
@@ -5060,47 +7837,101 @@
       <c r="E31" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F31" s="30"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="34"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="30"/>
-      <c r="N31" s="11"/>
-      <c r="O31" s="11"/>
-      <c r="P31" s="11"/>
-      <c r="Q31" s="11"/>
-      <c r="R31" s="34"/>
-      <c r="S31" s="11"/>
-      <c r="T31" s="30"/>
-      <c r="U31" s="11"/>
-      <c r="V31" s="31"/>
-      <c r="W31" s="11"/>
-      <c r="X31" s="11"/>
-      <c r="Y31" s="34"/>
-      <c r="Z31" s="11"/>
-      <c r="AA31" s="30"/>
-      <c r="AB31" s="11"/>
-      <c r="AC31" s="11"/>
-      <c r="AD31" s="11"/>
-      <c r="AE31" s="11"/>
-      <c r="AF31" s="34"/>
-      <c r="AG31" s="11"/>
-      <c r="AH31" s="11"/>
-      <c r="AI31" s="30"/>
-      <c r="AJ31" s="11"/>
+      <c r="F31" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G31" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H31" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I31" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J31" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="K31" s="25"/>
+      <c r="L31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R31" s="25"/>
+      <c r="S31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y31" s="25"/>
+      <c r="Z31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF31" s="25"/>
+      <c r="AG31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI31" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ31" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK31" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL31" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:42" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A32" s="12">
         <v>28</v>
       </c>
@@ -5114,47 +7945,101 @@
       <c r="E32" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F32" s="30"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="34"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="11"/>
-      <c r="P32" s="11"/>
-      <c r="Q32" s="11"/>
-      <c r="R32" s="34"/>
-      <c r="S32" s="11"/>
-      <c r="T32" s="30"/>
-      <c r="U32" s="11"/>
-      <c r="V32" s="31"/>
-      <c r="W32" s="11"/>
-      <c r="X32" s="11"/>
-      <c r="Y32" s="34"/>
-      <c r="Z32" s="11"/>
-      <c r="AA32" s="30"/>
-      <c r="AB32" s="11"/>
-      <c r="AC32" s="11"/>
-      <c r="AD32" s="11"/>
-      <c r="AE32" s="11"/>
-      <c r="AF32" s="34"/>
-      <c r="AG32" s="11"/>
-      <c r="AH32" s="11"/>
-      <c r="AI32" s="30"/>
-      <c r="AJ32" s="11"/>
+      <c r="F32" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="G32" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="H32" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I32" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J32" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="K32" s="25"/>
+      <c r="L32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P32" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R32" s="25"/>
+      <c r="S32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W32" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="X32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y32" s="25"/>
+      <c r="Z32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE32" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF32" s="25"/>
+      <c r="AG32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH32" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI32" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AJ32" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK32" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL32" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>29</v>
       </c>
@@ -5168,47 +8053,101 @@
       <c r="E33" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="30"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="34"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="30"/>
-      <c r="N33" s="11"/>
-      <c r="O33" s="11"/>
-      <c r="P33" s="11"/>
-      <c r="Q33" s="11"/>
-      <c r="R33" s="34"/>
-      <c r="S33" s="11"/>
-      <c r="T33" s="30"/>
-      <c r="U33" s="11"/>
-      <c r="V33" s="31"/>
-      <c r="W33" s="11"/>
-      <c r="X33" s="11"/>
-      <c r="Y33" s="34"/>
-      <c r="Z33" s="11"/>
-      <c r="AA33" s="30"/>
-      <c r="AB33" s="11"/>
-      <c r="AC33" s="11"/>
-      <c r="AD33" s="11"/>
-      <c r="AE33" s="11"/>
-      <c r="AF33" s="34"/>
-      <c r="AG33" s="11"/>
-      <c r="AH33" s="11"/>
-      <c r="AI33" s="30"/>
-      <c r="AJ33" s="11"/>
+      <c r="F33" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G33" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H33" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I33" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J33" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="K33" s="25"/>
+      <c r="L33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R33" s="25"/>
+      <c r="S33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y33" s="25"/>
+      <c r="Z33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF33" s="25"/>
+      <c r="AG33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ33" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK33" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL33" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A34" s="12">
         <v>30</v>
       </c>
@@ -5222,47 +8161,101 @@
       <c r="E34" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F34" s="30"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="30"/>
-      <c r="N34" s="11"/>
-      <c r="O34" s="11"/>
-      <c r="P34" s="11"/>
-      <c r="Q34" s="11"/>
-      <c r="R34" s="34"/>
-      <c r="S34" s="11"/>
-      <c r="T34" s="30"/>
-      <c r="U34" s="11"/>
-      <c r="V34" s="31"/>
-      <c r="W34" s="11"/>
-      <c r="X34" s="11"/>
-      <c r="Y34" s="34"/>
-      <c r="Z34" s="11"/>
-      <c r="AA34" s="30"/>
-      <c r="AB34" s="11"/>
-      <c r="AC34" s="11"/>
-      <c r="AD34" s="11"/>
-      <c r="AE34" s="11"/>
-      <c r="AF34" s="34"/>
-      <c r="AG34" s="11"/>
-      <c r="AH34" s="11"/>
-      <c r="AI34" s="30"/>
-      <c r="AJ34" s="11"/>
+      <c r="F34" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G34" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H34" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I34" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="J34" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="K34" s="25"/>
+      <c r="L34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R34" s="25"/>
+      <c r="S34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X34" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y34" s="25"/>
+      <c r="Z34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF34" s="25"/>
+      <c r="AG34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI34" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ34" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK34" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL34" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>31</v>
       </c>
@@ -5276,47 +8269,101 @@
       <c r="E35" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="30"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="34"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="30"/>
-      <c r="N35" s="11"/>
-      <c r="O35" s="11"/>
-      <c r="P35" s="11"/>
-      <c r="Q35" s="11"/>
-      <c r="R35" s="34"/>
-      <c r="S35" s="11"/>
-      <c r="T35" s="30"/>
-      <c r="U35" s="11"/>
-      <c r="V35" s="31"/>
-      <c r="W35" s="11"/>
-      <c r="X35" s="11"/>
-      <c r="Y35" s="34"/>
-      <c r="Z35" s="11"/>
-      <c r="AA35" s="30"/>
-      <c r="AB35" s="11"/>
-      <c r="AC35" s="11"/>
-      <c r="AD35" s="11"/>
-      <c r="AE35" s="11"/>
-      <c r="AF35" s="34"/>
-      <c r="AG35" s="11"/>
-      <c r="AH35" s="11"/>
-      <c r="AI35" s="30"/>
-      <c r="AJ35" s="11"/>
+      <c r="F35" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G35" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H35" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I35" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J35" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="K35" s="25"/>
+      <c r="L35" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N35" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O35" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="P35" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q35" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R35" s="25"/>
+      <c r="S35" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T35" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U35" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="V35" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="W35" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="X35" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y35" s="25"/>
+      <c r="Z35" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA35" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB35" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC35" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD35" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AE35" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF35" s="25"/>
+      <c r="AG35" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AH35" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI35" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ35" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK35" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AL35" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A36" s="12">
         <v>32</v>
       </c>
@@ -5330,53 +8377,104 @@
       <c r="E36" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F36" s="30"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="35"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="30"/>
-      <c r="N36" s="11"/>
-      <c r="O36" s="11"/>
-      <c r="P36" s="11"/>
-      <c r="Q36" s="11"/>
-      <c r="R36" s="35"/>
-      <c r="S36" s="11"/>
-      <c r="T36" s="30"/>
-      <c r="U36" s="11"/>
-      <c r="V36" s="31"/>
-      <c r="W36" s="11"/>
-      <c r="X36" s="11"/>
-      <c r="Y36" s="35"/>
-      <c r="Z36" s="11"/>
-      <c r="AA36" s="30"/>
-      <c r="AB36" s="11"/>
-      <c r="AC36" s="11"/>
-      <c r="AD36" s="11"/>
-      <c r="AE36" s="11"/>
-      <c r="AF36" s="35"/>
-      <c r="AG36" s="11"/>
-      <c r="AH36" s="11"/>
-      <c r="AI36" s="30"/>
-      <c r="AJ36" s="11"/>
+      <c r="F36" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="G36" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H36" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="I36" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="J36" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="K36" s="26"/>
+      <c r="L36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="N36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="O36" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="P36" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="R36" s="26"/>
+      <c r="S36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="T36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="V36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="W36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="X36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y36" s="26"/>
+      <c r="Z36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE36" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF36" s="26"/>
+      <c r="AG36" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI36" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ36" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="AK36" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL36" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="AL3:AL4"/>
-    <mergeCell ref="AM3:AN3"/>
-    <mergeCell ref="AM8:AP8"/>
-    <mergeCell ref="AM16:AP16"/>
+    <mergeCell ref="A2:AJ2"/>
+    <mergeCell ref="A1:AJ1"/>
     <mergeCell ref="K5:K36"/>
     <mergeCell ref="R5:R36"/>
     <mergeCell ref="Y5:Y36"/>
@@ -5386,15 +8484,18 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="A2:AJ2"/>
-    <mergeCell ref="A1:AJ1"/>
+    <mergeCell ref="AK3:AK4"/>
+    <mergeCell ref="AL3:AL4"/>
+    <mergeCell ref="AM3:AN3"/>
+    <mergeCell ref="AM8:AP8"/>
+    <mergeCell ref="AM16:AP16"/>
   </mergeCells>
-  <conditionalFormatting sqref="T5 V5 AA5 AI5 F5:M5 N5:Q36 U5:U36 W5:X36 AB5:AE36 AJ5:AJ36 G6:J36 L6:L36 S5:S36 R5 Z5:Z36 Y5 AG5:AH36 AF5 F4:AJ4">
+  <conditionalFormatting sqref="F4:AJ5 F6:J36 L6:Q36 S6:X36 Z6:AE36 AG6:AJ36">
     <cfRule type="expression" dxfId="5" priority="9">
       <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T5 V5 AA5 AI5 F5:M5 N5:Q36 U5:U36 W5:X36 AB5:AE36 AJ5:AJ36 G6:J36 L6:L36 S5:S36 R5 Z5:Z36 Y5 AG5:AH36 AF5">
+  <conditionalFormatting sqref="F5:AJ5 F6:J36 L6:Q36 S6:X36 Z6:AE36 AG6:AJ36">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"L"</formula>
     </cfRule>
@@ -5405,7 +8506,7 @@
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T5 V5 AA5 AI5 F5:M5 N5:Q36 U5:U36 W5:X36 AM4:AN4 AM5:AM6 AN9:AP9 AM9:AM12 AN17:AP17 AM17:AM20 AB5:AE36 AJ5:AJ36 G6:J36 L6:L36 S5:S36 R5 Z5:Z36 Y5 AG5:AH36 AF5 F3:AJ4">
+  <conditionalFormatting sqref="AM4:AN4 AM5:AM6 AN9:AP9 AM9:AM12 AN17:AP17 AM17:AM20 F3:AJ5 F6:J36 L6:Q36 S6:X36 Z6:AE36 AG6:AJ36">
     <cfRule type="expression" dxfId="1" priority="10">
       <formula>F$3="Sun"</formula>
     </cfRule>
